--- a/research/traditional_assets/database/data/philippines/philippines_information_services.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_information_services.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,25 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0512</v>
+        <v>-0.1255</v>
+      </c>
+      <c r="E2">
+        <v>0.374</v>
       </c>
       <c r="G2">
-        <v>-0.2609090909090909</v>
+        <v>-0.4651338107802488</v>
       </c>
       <c r="H2">
-        <v>-0.2609090909090909</v>
+        <v>-0.4651338107802488</v>
       </c>
       <c r="I2">
-        <v>-0.27</v>
+        <v>-0.816606812839362</v>
       </c>
       <c r="J2">
-        <v>-0.27</v>
+        <v>-0.7660314664248395</v>
       </c>
       <c r="K2">
-        <v>-1.52</v>
+        <v>-5.89</v>
       </c>
       <c r="L2">
-        <v>-0.1381818181818182</v>
+        <v>-0.7400427189345395</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>17.3</v>
+        <v>58.2</v>
       </c>
       <c r="V2">
-        <v>1.504347826086956</v>
+        <v>1.670973298880276</v>
       </c>
       <c r="W2">
-        <v>-0.05801526717557252</v>
+        <v>-0.1306559147903152</v>
       </c>
       <c r="X2">
-        <v>0.1861288007330958</v>
+        <v>0.2810446204176442</v>
       </c>
       <c r="Y2">
-        <v>-0.2441440679086683</v>
+        <v>-0.4117005352079594</v>
       </c>
       <c r="Z2">
-        <v>0.3956834532374101</v>
+        <v>0.1268530925022107</v>
       </c>
       <c r="AA2">
-        <v>-0.1068345323741007</v>
+        <v>-0.1170811344854213</v>
       </c>
       <c r="AB2">
-        <v>0.08341207011770696</v>
+        <v>0.1593456153281428</v>
       </c>
       <c r="AC2">
-        <v>-0.1902466024918077</v>
+        <v>-0.2764267498135642</v>
       </c>
       <c r="AD2">
-        <v>22.5</v>
+        <v>21.226</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.001868116942406726</v>
       </c>
       <c r="AF2">
-        <v>22.5</v>
+        <v>21.22786811694241</v>
       </c>
       <c r="AG2">
-        <v>5.199999999999999</v>
+        <v>-36.9721318830576</v>
       </c>
       <c r="AH2">
-        <v>0.6617647058823529</v>
+        <v>0.3786777633544486</v>
       </c>
       <c r="AI2">
-        <v>0.4912663755458516</v>
+        <v>0.1990836775772454</v>
       </c>
       <c r="AJ2">
-        <v>0.311377245508982</v>
+        <v>17.25950310318192</v>
       </c>
       <c r="AK2">
-        <v>0.1824561403508772</v>
+        <v>-0.7634474388543848</v>
       </c>
       <c r="AL2">
-        <v>0.111</v>
+        <v>0.119</v>
       </c>
       <c r="AM2">
-        <v>-0.09399999999999999</v>
+        <v>-1.053</v>
       </c>
       <c r="AN2">
-        <v>-8.152173913043478</v>
+        <v>-3.452504879635654</v>
       </c>
       <c r="AO2">
-        <v>-26.75675675675676</v>
+        <v>-54.63025210084034</v>
       </c>
       <c r="AP2">
-        <v>-1.884057971014493</v>
+        <v>6.013684431206507</v>
       </c>
       <c r="AQ2">
-        <v>31.59574468085107</v>
+        <v>6.173789173789174</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I-Remit, Inc. (PSE:I)</t>
+          <t>Paxys, Inc. (PSE:PAX)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,25 +719,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0512</v>
+        <v>-0.133</v>
+      </c>
+      <c r="E3">
+        <v>0.374</v>
       </c>
       <c r="G3">
-        <v>-0.2609090909090909</v>
+        <v>-1.251088534107402</v>
       </c>
       <c r="H3">
-        <v>-0.2609090909090909</v>
+        <v>-1.251088534107402</v>
       </c>
       <c r="I3">
-        <v>-0.27</v>
+        <v>-1.406928335832339</v>
       </c>
       <c r="J3">
-        <v>-0.27</v>
+        <v>-1.232656245895403</v>
       </c>
       <c r="K3">
-        <v>-1.52</v>
+        <v>0.29</v>
       </c>
       <c r="L3">
-        <v>-0.1381818181818182</v>
+        <v>0.420899854862119</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +749,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +758,207 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
+        <v>40.9</v>
+      </c>
+      <c r="V3">
+        <v>1.531835205992509</v>
+      </c>
+      <c r="W3">
+        <v>0.003924221921515561</v>
+      </c>
+      <c r="X3">
+        <v>0.1646380118878168</v>
+      </c>
+      <c r="Y3">
+        <v>-0.1607137899663012</v>
+      </c>
+      <c r="Z3">
+        <v>0.01886540956212408</v>
+      </c>
+      <c r="AA3">
+        <v>-0.0232545649281271</v>
+      </c>
+      <c r="AB3">
+        <v>0.1620718821964457</v>
+      </c>
+      <c r="AC3">
+        <v>-0.1853264471245729</v>
+      </c>
+      <c r="AD3">
+        <v>0.626</v>
+      </c>
+      <c r="AE3">
+        <v>0.001868116942406726</v>
+      </c>
+      <c r="AF3">
+        <v>0.6278681169424067</v>
+      </c>
+      <c r="AG3">
+        <v>-40.27213188305759</v>
+      </c>
+      <c r="AH3">
+        <v>0.02297537862286259</v>
+      </c>
+      <c r="AI3">
+        <v>0.008864704439582267</v>
+      </c>
+      <c r="AJ3">
+        <v>2.967266471476764</v>
+      </c>
+      <c r="AK3">
+        <v>-1.345639847305368</v>
+      </c>
+      <c r="AL3">
+        <v>0.033</v>
+      </c>
+      <c r="AM3">
+        <v>-0.997</v>
+      </c>
+      <c r="AN3">
+        <v>-0.9098837209302326</v>
+      </c>
+      <c r="AO3">
+        <v>-29.42424242424242</v>
+      </c>
+      <c r="AP3">
+        <v>58.53507541142092</v>
+      </c>
+      <c r="AQ3">
+        <v>0.9739217652958876</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>I-Remit, Inc. (PSE:I)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Information Services</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.118</v>
+      </c>
+      <c r="G4">
+        <v>-0.390646492434663</v>
+      </c>
+      <c r="H4">
+        <v>-0.390646492434663</v>
+      </c>
+      <c r="I4">
+        <v>-0.7606602475928474</v>
+      </c>
+      <c r="J4">
+        <v>-0.7606602475928474</v>
+      </c>
+      <c r="K4">
+        <v>-6.18</v>
+      </c>
+      <c r="L4">
+        <v>-0.8500687757909217</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
         <v>17.3</v>
       </c>
-      <c r="V3">
-        <v>1.504347826086956</v>
-      </c>
-      <c r="W3">
-        <v>-0.05801526717557252</v>
-      </c>
-      <c r="X3">
-        <v>0.1861288007330958</v>
-      </c>
-      <c r="Y3">
-        <v>-0.2441440679086683</v>
-      </c>
-      <c r="Z3">
-        <v>0.3956834532374101</v>
-      </c>
-      <c r="AA3">
-        <v>-0.1068345323741007</v>
-      </c>
-      <c r="AB3">
-        <v>0.08341207011770696</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1902466024918077</v>
-      </c>
-      <c r="AD3">
-        <v>22.5</v>
-      </c>
-      <c r="AE3">
+      <c r="V4">
+        <v>2.127921279212792</v>
+      </c>
+      <c r="W4">
+        <v>-0.2652360515021459</v>
+      </c>
+      <c r="X4">
+        <v>0.3974512289474715</v>
+      </c>
+      <c r="Y4">
+        <v>-0.6626872804496174</v>
+      </c>
+      <c r="Z4">
+        <v>0.2772692601067888</v>
+      </c>
+      <c r="AA4">
+        <v>-0.2109077040427155</v>
+      </c>
+      <c r="AB4">
+        <v>0.1566193484598399</v>
+      </c>
+      <c r="AC4">
+        <v>-0.3675270525025555</v>
+      </c>
+      <c r="AD4">
+        <v>20.6</v>
+      </c>
+      <c r="AE4">
         <v>0</v>
       </c>
-      <c r="AF3">
-        <v>22.5</v>
-      </c>
-      <c r="AG3">
-        <v>5.199999999999999</v>
-      </c>
-      <c r="AH3">
-        <v>0.6617647058823529</v>
-      </c>
-      <c r="AI3">
-        <v>0.4912663755458516</v>
-      </c>
-      <c r="AJ3">
-        <v>0.311377245508982</v>
-      </c>
-      <c r="AK3">
-        <v>0.1824561403508772</v>
-      </c>
-      <c r="AL3">
-        <v>0.111</v>
-      </c>
-      <c r="AM3">
-        <v>-0.09399999999999999</v>
-      </c>
-      <c r="AN3">
-        <v>-8.152173913043478</v>
-      </c>
-      <c r="AO3">
-        <v>-26.75675675675676</v>
-      </c>
-      <c r="AP3">
-        <v>-1.884057971014493</v>
-      </c>
-      <c r="AQ3">
-        <v>31.59574468085107</v>
+      <c r="AF4">
+        <v>20.6</v>
+      </c>
+      <c r="AG4">
+        <v>3.300000000000001</v>
+      </c>
+      <c r="AH4">
+        <v>0.7170205360250609</v>
+      </c>
+      <c r="AI4">
+        <v>0.5754189944134079</v>
+      </c>
+      <c r="AJ4">
+        <v>0.2887139107611549</v>
+      </c>
+      <c r="AK4">
+        <v>0.1783783783783784</v>
+      </c>
+      <c r="AL4">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="AM4">
+        <v>-0.05599999999999999</v>
+      </c>
+      <c r="AN4">
+        <v>-3.772893772893773</v>
+      </c>
+      <c r="AO4">
+        <v>-64.30232558139535</v>
+      </c>
+      <c r="AP4">
+        <v>-0.6043956043956046</v>
+      </c>
+      <c r="AQ4">
+        <v>98.75000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/philippines/philippines_information_services.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_information_services.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.1255</v>
+        <v>-0.351</v>
       </c>
       <c r="E2">
-        <v>0.374</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="G2">
-        <v>-0.4651338107802488</v>
+        <v>-6.936416184971098</v>
       </c>
       <c r="H2">
-        <v>-0.4651338107802488</v>
+        <v>-6.936416184971098</v>
       </c>
       <c r="I2">
-        <v>-0.816606812839362</v>
+        <v>-8.265895953757227</v>
       </c>
       <c r="J2">
-        <v>-0.7660314664248395</v>
+        <v>-7.786382652572414</v>
       </c>
       <c r="K2">
-        <v>-5.89</v>
+        <v>1.71</v>
       </c>
       <c r="L2">
-        <v>-0.7400427189345395</v>
+        <v>9.884393063583815</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +627,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>58.2</v>
+        <v>42.5</v>
       </c>
       <c r="V2">
-        <v>1.670973298880276</v>
+        <v>2.560240963855422</v>
       </c>
       <c r="W2">
-        <v>-0.1306559147903152</v>
+        <v>0.02435897435897436</v>
       </c>
       <c r="X2">
-        <v>0.2810446204176442</v>
+        <v>0.1158204990188526</v>
       </c>
       <c r="Y2">
-        <v>-0.4117005352079594</v>
+        <v>-0.0914615246598782</v>
       </c>
       <c r="Z2">
-        <v>0.1268530925022107</v>
+        <v>0.005780926284835926</v>
       </c>
       <c r="AA2">
-        <v>-0.1170811344854213</v>
+        <v>-0.04501250414004635</v>
       </c>
       <c r="AB2">
-        <v>0.1593456153281428</v>
+        <v>0.1140012329305232</v>
       </c>
       <c r="AC2">
-        <v>-0.2764267498135642</v>
+        <v>-0.1590137370705695</v>
       </c>
       <c r="AD2">
-        <v>21.226</v>
+        <v>0.518</v>
       </c>
       <c r="AE2">
-        <v>0.001868116942406726</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>21.22786811694241</v>
+        <v>0.518</v>
       </c>
       <c r="AG2">
-        <v>-36.9721318830576</v>
+        <v>-41.982</v>
       </c>
       <c r="AH2">
-        <v>0.3786777633544486</v>
+        <v>0.03026054445612805</v>
       </c>
       <c r="AI2">
-        <v>0.1990836775772454</v>
+        <v>0.007084438852266201</v>
       </c>
       <c r="AJ2">
-        <v>17.25950310318192</v>
+        <v>1.654006776455756</v>
       </c>
       <c r="AK2">
-        <v>-0.7634474388543848</v>
+        <v>-1.371154223006075</v>
       </c>
       <c r="AL2">
-        <v>0.119</v>
+        <v>0.029</v>
       </c>
       <c r="AM2">
-        <v>-1.053</v>
+        <v>-3.011</v>
       </c>
       <c r="AN2">
-        <v>-3.452504879635654</v>
+        <v>-0.3647887323943662</v>
       </c>
       <c r="AO2">
-        <v>-54.63025210084034</v>
+        <v>-49.3103448275862</v>
       </c>
       <c r="AP2">
-        <v>6.013684431206507</v>
+        <v>29.56478873239437</v>
       </c>
       <c r="AQ2">
-        <v>6.173789173789174</v>
+        <v>0.4749252739953503</v>
       </c>
     </row>
     <row r="3">
@@ -719,28 +719,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.133</v>
+        <v>-0.351</v>
       </c>
       <c r="E3">
-        <v>0.374</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="G3">
-        <v>-1.251088534107402</v>
+        <v>-6.936416184971098</v>
       </c>
       <c r="H3">
-        <v>-1.251088534107402</v>
+        <v>-6.936416184971098</v>
       </c>
       <c r="I3">
-        <v>-1.406928335832339</v>
+        <v>-8.265895953757227</v>
       </c>
       <c r="J3">
-        <v>-1.232656245895403</v>
+        <v>-7.786382652572414</v>
       </c>
       <c r="K3">
-        <v>0.29</v>
+        <v>1.71</v>
       </c>
       <c r="L3">
-        <v>0.420899854862119</v>
+        <v>9.884393063583815</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,201 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>40.9</v>
+        <v>42.5</v>
       </c>
       <c r="V3">
-        <v>1.531835205992509</v>
+        <v>2.560240963855422</v>
       </c>
       <c r="W3">
-        <v>0.003924221921515561</v>
+        <v>0.02435897435897436</v>
       </c>
       <c r="X3">
-        <v>0.1646380118878168</v>
+        <v>0.1158204990188526</v>
       </c>
       <c r="Y3">
-        <v>-0.1607137899663012</v>
+        <v>-0.0914615246598782</v>
       </c>
       <c r="Z3">
-        <v>0.01886540956212408</v>
+        <v>0.005780926284835926</v>
       </c>
       <c r="AA3">
-        <v>-0.0232545649281271</v>
+        <v>-0.04501250414004635</v>
       </c>
       <c r="AB3">
-        <v>0.1620718821964457</v>
+        <v>0.1140012329305232</v>
       </c>
       <c r="AC3">
-        <v>-0.1853264471245729</v>
+        <v>-0.1590137370705695</v>
       </c>
       <c r="AD3">
-        <v>0.626</v>
+        <v>0.518</v>
       </c>
       <c r="AE3">
-        <v>0.001868116942406726</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.6278681169424067</v>
+        <v>0.518</v>
       </c>
       <c r="AG3">
-        <v>-40.27213188305759</v>
+        <v>-41.982</v>
       </c>
       <c r="AH3">
-        <v>0.02297537862286259</v>
+        <v>0.03026054445612805</v>
       </c>
       <c r="AI3">
-        <v>0.008864704439582267</v>
+        <v>0.007084438852266201</v>
       </c>
       <c r="AJ3">
-        <v>2.967266471476764</v>
+        <v>1.654006776455756</v>
       </c>
       <c r="AK3">
-        <v>-1.345639847305368</v>
+        <v>-1.371154223006075</v>
       </c>
       <c r="AL3">
-        <v>0.033</v>
+        <v>0.029</v>
       </c>
       <c r="AM3">
-        <v>-0.997</v>
+        <v>-3.011</v>
       </c>
       <c r="AN3">
-        <v>-0.9098837209302326</v>
+        <v>-0.3647887323943662</v>
       </c>
       <c r="AO3">
-        <v>-29.42424242424242</v>
+        <v>-49.3103448275862</v>
       </c>
       <c r="AP3">
-        <v>58.53507541142092</v>
+        <v>29.56478873239437</v>
       </c>
       <c r="AQ3">
-        <v>0.9739217652958876</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>I-Remit, Inc. (PSE:I)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Information Services</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>-0.118</v>
-      </c>
-      <c r="G4">
-        <v>-0.390646492434663</v>
-      </c>
-      <c r="H4">
-        <v>-0.390646492434663</v>
-      </c>
-      <c r="I4">
-        <v>-0.7606602475928474</v>
-      </c>
-      <c r="J4">
-        <v>-0.7606602475928474</v>
-      </c>
-      <c r="K4">
-        <v>-6.18</v>
-      </c>
-      <c r="L4">
-        <v>-0.8500687757909217</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>17.3</v>
-      </c>
-      <c r="V4">
-        <v>2.127921279212792</v>
-      </c>
-      <c r="W4">
-        <v>-0.2652360515021459</v>
-      </c>
-      <c r="X4">
-        <v>0.3974512289474715</v>
-      </c>
-      <c r="Y4">
-        <v>-0.6626872804496174</v>
-      </c>
-      <c r="Z4">
-        <v>0.2772692601067888</v>
-      </c>
-      <c r="AA4">
-        <v>-0.2109077040427155</v>
-      </c>
-      <c r="AB4">
-        <v>0.1566193484598399</v>
-      </c>
-      <c r="AC4">
-        <v>-0.3675270525025555</v>
-      </c>
-      <c r="AD4">
-        <v>20.6</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>20.6</v>
-      </c>
-      <c r="AG4">
-        <v>3.300000000000001</v>
-      </c>
-      <c r="AH4">
-        <v>0.7170205360250609</v>
-      </c>
-      <c r="AI4">
-        <v>0.5754189944134079</v>
-      </c>
-      <c r="AJ4">
-        <v>0.2887139107611549</v>
-      </c>
-      <c r="AK4">
-        <v>0.1783783783783784</v>
-      </c>
-      <c r="AL4">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="AM4">
-        <v>-0.05599999999999999</v>
-      </c>
-      <c r="AN4">
-        <v>-3.772893772893773</v>
-      </c>
-      <c r="AO4">
-        <v>-64.30232558139535</v>
-      </c>
-      <c r="AP4">
-        <v>-0.6043956043956046</v>
-      </c>
-      <c r="AQ4">
-        <v>98.75000000000001</v>
+        <v>0.4749252739953503</v>
       </c>
     </row>
   </sheetData>
